--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260831_232950.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260831_232950.xlsx
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260831_232950.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260831_232950.xlsx
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
